--- a/output_data/charts/0500000US39091.xlsx
+++ b/output_data/charts/0500000US39091.xlsx
@@ -167,10 +167,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -212,16 +212,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$15</c:f>
+              <c:f>Sheet1!$B$2:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.5246704413790088</c:v>
                 </c:pt>
@@ -253,16 +256,19 @@
                   <c:v>0.7566785103303066</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.858704137392662</c:v>
+                  <c:v>0.8587413800581167</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.8839204471597556</c:v>
+                  <c:v>0.8838821490467937</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.8901046415700578</c:v>
+                  <c:v>0.9100781928757603</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.9466530603382765</c:v>
+                  <c:v>0.9707894451080464</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.041553650862536</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -292,10 +298,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -337,16 +343,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$15</c:f>
+              <c:f>Sheet1!$C$2:$C$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.611175480401373</c:v>
                 </c:pt>
@@ -378,16 +387,19 @@
                   <c:v>1.754616835548537</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.806314511232544</c:v>
+                  <c:v>1.806392852495988</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.876164478530266</c:v>
+                  <c:v>1.873916811091854</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.908297512048977</c:v>
+                  <c:v>1.904865334491746</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.945415463447467</c:v>
+                  <c:v>1.943750678683896</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.037539329499837</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -417,10 +429,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -462,16 +474,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$15</c:f>
+              <c:f>Sheet1!$D$2:$D$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.171763985746453</c:v>
                 </c:pt>
@@ -503,16 +518,19 @@
                   <c:v>2.059481510725095</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.16410790181282</c:v>
+                  <c:v>2.166370299692067</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.270462325057411</c:v>
+                  <c:v>2.272530329289428</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.303417133428857</c:v>
+                  <c:v>2.300173761946134</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.357947760383872</c:v>
+                  <c:v>2.410685199261592</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.593034609959857</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -542,10 +560,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -587,16 +605,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$15</c:f>
+              <c:f>Sheet1!$E$2:$E$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.2645213475285836</c:v>
                 </c:pt>
@@ -628,16 +649,19 @@
                   <c:v>0.307057946220994</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.3187613843351548</c:v>
+                  <c:v>0.3187752092639979</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.3358031110533385</c:v>
+                  <c:v>0.33578856152513</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.3603838304893405</c:v>
+                  <c:v>0.3583840139009557</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.3712790672427644</c:v>
+                  <c:v>0.3670322510587469</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.3645437778018878</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -667,10 +691,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -712,16 +736,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$15</c:f>
+              <c:f>Sheet1!$F$2:$F$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.759832105458759</c:v>
                 </c:pt>
@@ -753,16 +780,19 @@
                   <c:v>2.177918147124622</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.187960794518172</c:v>
+                  <c:v>2.188055688077374</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.253130551583691</c:v>
+                  <c:v>2.253032928942808</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.24914246016239</c:v>
+                  <c:v>2.248045178105995</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.255900297457499</c:v>
+                  <c:v>2.241285698772939</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.347835521319301</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -792,10 +822,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -837,16 +867,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$2:$G$15</c:f>
+              <c:f>Sheet1!$G$2:$G$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>94.66803663948582</c:v>
                 </c:pt>
@@ -878,16 +911,19 @@
                   <c:v>92.94424705005045</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>92.66415127070864</c:v>
+                  <c:v>92.66166457041246</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>92.38051908661554</c:v>
+                  <c:v>92.38084922010398</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>92.28865442230038</c:v>
+                  <c:v>92.2784535186794</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>92.12280435113011</c:v>
+                  <c:v>92.06645672711477</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>91.61549311055659</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1006,13 +1042,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1428750</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1320,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" style="1" customWidth="1"/>
@@ -1590,22 +1626,22 @@
         <v>2020</v>
       </c>
       <c r="B12" s="2">
-        <v>0.858704137392662</v>
+        <v>0.8587413800581167</v>
       </c>
       <c r="C12" s="2">
-        <v>1.806314511232544</v>
+        <v>1.806392852495988</v>
       </c>
       <c r="D12" s="2">
-        <v>2.16410790181282</v>
+        <v>2.166370299692067</v>
       </c>
       <c r="E12" s="2">
-        <v>0.3187613843351548</v>
+        <v>0.3187752092639979</v>
       </c>
       <c r="F12" s="2">
-        <v>2.187960794518172</v>
+        <v>2.188055688077374</v>
       </c>
       <c r="G12" s="2">
-        <v>92.66415127070864</v>
+        <v>92.66166457041246</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1613,22 +1649,22 @@
         <v>2021</v>
       </c>
       <c r="B13" s="2">
-        <v>0.8839204471597556</v>
+        <v>0.8838821490467937</v>
       </c>
       <c r="C13" s="2">
-        <v>1.876164478530266</v>
+        <v>1.873916811091854</v>
       </c>
       <c r="D13" s="2">
-        <v>2.270462325057411</v>
+        <v>2.272530329289428</v>
       </c>
       <c r="E13" s="2">
-        <v>0.3358031110533385</v>
+        <v>0.33578856152513</v>
       </c>
       <c r="F13" s="2">
-        <v>2.253130551583691</v>
+        <v>2.253032928942808</v>
       </c>
       <c r="G13" s="2">
-        <v>92.38051908661554</v>
+        <v>92.38084922010398</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1636,22 +1672,22 @@
         <v>2022</v>
       </c>
       <c r="B14" s="2">
-        <v>0.8901046415700578</v>
+        <v>0.9100781928757603</v>
       </c>
       <c r="C14" s="2">
-        <v>1.908297512048977</v>
+        <v>1.904865334491746</v>
       </c>
       <c r="D14" s="2">
-        <v>2.303417133428857</v>
+        <v>2.300173761946134</v>
       </c>
       <c r="E14" s="2">
-        <v>0.3603838304893405</v>
+        <v>0.3583840139009557</v>
       </c>
       <c r="F14" s="2">
-        <v>2.24914246016239</v>
+        <v>2.248045178105995</v>
       </c>
       <c r="G14" s="2">
-        <v>92.28865442230038</v>
+        <v>92.2784535186794</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1659,22 +1695,45 @@
         <v>2023</v>
       </c>
       <c r="B15" s="2">
-        <v>0.9466530603382765</v>
+        <v>0.9707894451080464</v>
       </c>
       <c r="C15" s="2">
-        <v>1.945415463447467</v>
+        <v>1.943750678683896</v>
       </c>
       <c r="D15" s="2">
-        <v>2.357947760383872</v>
+        <v>2.410685199261592</v>
       </c>
       <c r="E15" s="2">
-        <v>0.3712790672427644</v>
+        <v>0.3670322510587469</v>
       </c>
       <c r="F15" s="2">
-        <v>2.255900297457499</v>
+        <v>2.241285698772939</v>
       </c>
       <c r="G15" s="2">
-        <v>92.12280435113011</v>
+        <v>92.06645672711477</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1.041553650862536</v>
+      </c>
+      <c r="C16" s="2">
+        <v>2.037539329499837</v>
+      </c>
+      <c r="D16" s="2">
+        <v>2.593034609959857</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.3645437778018878</v>
+      </c>
+      <c r="F16" s="2">
+        <v>2.347835521319301</v>
+      </c>
+      <c r="G16" s="2">
+        <v>91.61549311055659</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/0500000US39091.xlsx
+++ b/output_data/charts/0500000US39091.xlsx
@@ -229,31 +229,31 @@
                   <c:v>0.5246704413790088</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.5873972602739727</c:v>
+                  <c:v>0.5874230103237402</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.5989606271470096</c:v>
+                  <c:v>0.5989870072671217</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.6674155818410097</c:v>
+                  <c:v>0.6653008173066332</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.723442619346043</c:v>
+                  <c:v>0.7213071492973853</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.6850071815269031</c:v>
+                  <c:v>0.6850828729281767</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.7066120279100675</c:v>
+                  <c:v>0.6957986172664421</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.7607758144060862</c:v>
+                  <c:v>0.7367582636399841</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.7749884082930383</c:v>
+                  <c:v>0.7389923233036266</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.7566785103303066</c:v>
+                  <c:v>0.711595726046593</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.8587413800581167</c:v>
@@ -360,31 +360,31 @@
                   <c:v>1.611175480401373</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.547397260273973</c:v>
+                  <c:v>1.547465094360301</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.614110807716022</c:v>
+                  <c:v>1.6185862144902</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.711491442542787</c:v>
+                  <c:v>1.713920648558148</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.743738593134991</c:v>
+                  <c:v>1.748290194181162</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.734614959672964</c:v>
+                  <c:v>1.737016574585635</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.732196256506811</c:v>
+                  <c:v>1.721769189859954</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.778092310414225</c:v>
+                  <c:v>1.756714898889331</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.761939458170498</c:v>
+                  <c:v>1.742698314656313</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.754616835548537</c:v>
+                  <c:v>1.755999299351901</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>1.806392852495988</c:v>
@@ -491,31 +491,31 @@
                   <c:v>1.171763985746453</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.255890410958904</c:v>
+                  <c:v>1.262521096815203</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.272791332687395</c:v>
+                  <c:v>1.283858181017397</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.339236547060508</c:v>
+                  <c:v>1.352631463000903</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.405105877696418</c:v>
+                  <c:v>1.42062322696985</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.447353883548779</c:v>
+                  <c:v>1.469613259668508</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.492967105991804</c:v>
+                  <c:v>1.504609111859599</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.521551628812172</c:v>
+                  <c:v>1.533253683791318</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.585303923516813</c:v>
+                  <c:v>1.59710579722933</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.059481510725095</c:v>
+                  <c:v>2.053774741636013</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>2.166370299692067</c:v>
@@ -622,31 +622,31 @@
                   <c:v>0.2645213475285836</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.252054794520548</c:v>
+                  <c:v>0.2564495977905881</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2620452743768167</c:v>
+                  <c:v>0.2664611319092711</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2797418445340206</c:v>
+                  <c:v>0.2841847862005155</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2946544407062911</c:v>
+                  <c:v>0.2990785740989158</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.320406584907745</c:v>
+                  <c:v>0.3248618784530387</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3344777937756119</c:v>
+                  <c:v>0.3412515511434143</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3184642944025478</c:v>
+                  <c:v>0.3208106553387318</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3179439623766311</c:v>
+                  <c:v>0.3242742433600988</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.307057946220994</c:v>
+                  <c:v>0.3087230688386758</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.3187752092639979</c:v>
@@ -750,34 +750,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.759832105458759</c:v>
+                  <c:v>1.764204359136917</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.808219178082192</c:v>
+                  <c:v>1.817065953576047</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.836518981766934</c:v>
+                  <c:v>1.845408500330324</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.92515253639948</c:v>
+                  <c:v>1.945233846628335</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.932845174483805</c:v>
+                  <c:v>1.955006267455413</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.948955916473318</c:v>
+                  <c:v>1.975690607734807</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.082179643371359</c:v>
+                  <c:v>2.111770962595284</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.063383240816507</c:v>
+                  <c:v>2.088587990619054</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.084299308913471</c:v>
+                  <c:v>2.102267713756287</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.177918147124622</c:v>
+                  <c:v>2.19390436153442</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>2.188055688077374</c:v>
@@ -881,34 +881,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>94.66803663948582</c:v>
+                  <c:v>94.66366438580766</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>94.5490410958904</c:v>
+                  <c:v>94.52907524713412</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>94.41557297630581</c:v>
+                  <c:v>94.38669896498568</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>94.07696204762219</c:v>
+                  <c:v>94.03872843830547</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>93.90021329463245</c:v>
+                  <c:v>93.85569458799728</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>93.86366147387028</c:v>
+                  <c:v>93.80773480662984</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>93.65156717244435</c:v>
+                  <c:v>93.6248005672753</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>93.55773271114846</c:v>
+                  <c:v>93.56387450772158</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>93.47552493872955</c:v>
+                  <c:v>93.49466160769434</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>92.94424705005045</c:v>
+                  <c:v>92.97600280259239</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>92.66166457041246</c:v>
@@ -1408,10 +1408,10 @@
         <v>0.2645213475285836</v>
       </c>
       <c r="F2" s="2">
-        <v>1.759832105458759</v>
+        <v>1.764204359136917</v>
       </c>
       <c r="G2" s="2">
-        <v>94.66803663948582</v>
+        <v>94.66366438580766</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1419,22 +1419,22 @@
         <v>2011</v>
       </c>
       <c r="B3" s="2">
-        <v>0.5873972602739727</v>
+        <v>0.5874230103237402</v>
       </c>
       <c r="C3" s="2">
-        <v>1.547397260273973</v>
+        <v>1.547465094360301</v>
       </c>
       <c r="D3" s="2">
-        <v>1.255890410958904</v>
+        <v>1.262521096815203</v>
       </c>
       <c r="E3" s="2">
-        <v>0.252054794520548</v>
+        <v>0.2564495977905881</v>
       </c>
       <c r="F3" s="2">
-        <v>1.808219178082192</v>
+        <v>1.817065953576047</v>
       </c>
       <c r="G3" s="2">
-        <v>94.5490410958904</v>
+        <v>94.52907524713412</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1442,22 +1442,22 @@
         <v>2012</v>
       </c>
       <c r="B4" s="2">
-        <v>0.5989606271470096</v>
+        <v>0.5989870072671217</v>
       </c>
       <c r="C4" s="2">
-        <v>1.614110807716022</v>
+        <v>1.6185862144902</v>
       </c>
       <c r="D4" s="2">
-        <v>1.272791332687395</v>
+        <v>1.283858181017397</v>
       </c>
       <c r="E4" s="2">
-        <v>0.2620452743768167</v>
+        <v>0.2664611319092711</v>
       </c>
       <c r="F4" s="2">
-        <v>1.836518981766934</v>
+        <v>1.845408500330324</v>
       </c>
       <c r="G4" s="2">
-        <v>94.41557297630581</v>
+        <v>94.38669896498568</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1465,22 +1465,22 @@
         <v>2013</v>
       </c>
       <c r="B5" s="2">
-        <v>0.6674155818410097</v>
+        <v>0.6653008173066332</v>
       </c>
       <c r="C5" s="2">
-        <v>1.711491442542787</v>
+        <v>1.713920648558148</v>
       </c>
       <c r="D5" s="2">
-        <v>1.339236547060508</v>
+        <v>1.352631463000903</v>
       </c>
       <c r="E5" s="2">
-        <v>0.2797418445340206</v>
+        <v>0.2841847862005155</v>
       </c>
       <c r="F5" s="2">
-        <v>1.92515253639948</v>
+        <v>1.945233846628335</v>
       </c>
       <c r="G5" s="2">
-        <v>94.07696204762219</v>
+        <v>94.03872843830547</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1488,22 +1488,22 @@
         <v>2014</v>
       </c>
       <c r="B6" s="2">
-        <v>0.723442619346043</v>
+        <v>0.7213071492973853</v>
       </c>
       <c r="C6" s="2">
-        <v>1.743738593134991</v>
+        <v>1.748290194181162</v>
       </c>
       <c r="D6" s="2">
-        <v>1.405105877696418</v>
+        <v>1.42062322696985</v>
       </c>
       <c r="E6" s="2">
-        <v>0.2946544407062911</v>
+        <v>0.2990785740989158</v>
       </c>
       <c r="F6" s="2">
-        <v>1.932845174483805</v>
+        <v>1.955006267455413</v>
       </c>
       <c r="G6" s="2">
-        <v>93.90021329463245</v>
+        <v>93.85569458799728</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1511,22 +1511,22 @@
         <v>2015</v>
       </c>
       <c r="B7" s="2">
-        <v>0.6850071815269031</v>
+        <v>0.6850828729281767</v>
       </c>
       <c r="C7" s="2">
-        <v>1.734614959672964</v>
+        <v>1.737016574585635</v>
       </c>
       <c r="D7" s="2">
-        <v>1.447353883548779</v>
+        <v>1.469613259668508</v>
       </c>
       <c r="E7" s="2">
-        <v>0.320406584907745</v>
+        <v>0.3248618784530387</v>
       </c>
       <c r="F7" s="2">
-        <v>1.948955916473318</v>
+        <v>1.975690607734807</v>
       </c>
       <c r="G7" s="2">
-        <v>93.86366147387028</v>
+        <v>93.80773480662984</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1534,22 +1534,22 @@
         <v>2016</v>
       </c>
       <c r="B8" s="2">
-        <v>0.7066120279100675</v>
+        <v>0.6957986172664421</v>
       </c>
       <c r="C8" s="2">
-        <v>1.732196256506811</v>
+        <v>1.721769189859954</v>
       </c>
       <c r="D8" s="2">
-        <v>1.492967105991804</v>
+        <v>1.504609111859599</v>
       </c>
       <c r="E8" s="2">
-        <v>0.3344777937756119</v>
+        <v>0.3412515511434143</v>
       </c>
       <c r="F8" s="2">
-        <v>2.082179643371359</v>
+        <v>2.111770962595284</v>
       </c>
       <c r="G8" s="2">
-        <v>93.65156717244435</v>
+        <v>93.6248005672753</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1557,22 +1557,22 @@
         <v>2017</v>
       </c>
       <c r="B9" s="2">
-        <v>0.7607758144060862</v>
+        <v>0.7367582636399841</v>
       </c>
       <c r="C9" s="2">
-        <v>1.778092310414225</v>
+        <v>1.756714898889331</v>
       </c>
       <c r="D9" s="2">
-        <v>1.521551628812172</v>
+        <v>1.533253683791318</v>
       </c>
       <c r="E9" s="2">
-        <v>0.3184642944025478</v>
+        <v>0.3208106553387318</v>
       </c>
       <c r="F9" s="2">
-        <v>2.063383240816507</v>
+        <v>2.088587990619054</v>
       </c>
       <c r="G9" s="2">
-        <v>93.55773271114846</v>
+        <v>93.56387450772158</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1580,22 +1580,22 @@
         <v>2018</v>
       </c>
       <c r="B10" s="2">
-        <v>0.7749884082930383</v>
+        <v>0.7389923233036266</v>
       </c>
       <c r="C10" s="2">
-        <v>1.761939458170498</v>
+        <v>1.742698314656313</v>
       </c>
       <c r="D10" s="2">
-        <v>1.585303923516813</v>
+        <v>1.59710579722933</v>
       </c>
       <c r="E10" s="2">
-        <v>0.3179439623766311</v>
+        <v>0.3242742433600988</v>
       </c>
       <c r="F10" s="2">
-        <v>2.084299308913471</v>
+        <v>2.102267713756287</v>
       </c>
       <c r="G10" s="2">
-        <v>93.47552493872955</v>
+        <v>93.49466160769434</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1603,22 +1603,22 @@
         <v>2019</v>
       </c>
       <c r="B11" s="2">
-        <v>0.7566785103303066</v>
+        <v>0.711595726046593</v>
       </c>
       <c r="C11" s="2">
-        <v>1.754616835548537</v>
+        <v>1.755999299351901</v>
       </c>
       <c r="D11" s="2">
-        <v>2.059481510725095</v>
+        <v>2.053774741636013</v>
       </c>
       <c r="E11" s="2">
-        <v>0.307057946220994</v>
+        <v>0.3087230688386758</v>
       </c>
       <c r="F11" s="2">
-        <v>2.177918147124622</v>
+        <v>2.19390436153442</v>
       </c>
       <c r="G11" s="2">
-        <v>92.94424705005045</v>
+        <v>92.97600280259239</v>
       </c>
     </row>
     <row r="12" spans="1:7">
